--- a/docs/PRAP_Programming_Specification_v1.27.xlsx
+++ b/docs/PRAP_Programming_Specification_v1.27.xlsx
@@ -3291,7 +3291,7 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>R-45, REQ-DSH-16. Five screen changes, no rule and no figure. Sheet 06 records the four that are drawing decisions. A CHART WHOSE X AXIS IS THE HORIZON takes its width from the month count - W = max(Wmin, padL + padR + months x Wper) - and its panel scrolls; the two utilisation charts were the last fixed-width ones, and a fixed width is legible only over the span it was chosen for and fails silently outside it. Wper is chosen so the DEFAULT horizon still falls under Wmin, which is what keeps the change invisible to the view almost everybody opens on. PANELS ARE TILED ONLY WHERE BOTH ARE NARROW: the person tab's three wide tables are one column, in work order. A PANEL THAT IS A CHILD OF A SELECTION names its parent from one shared helper, so two panels stating the same assignment cannot drift. LEGEND PICKING is recorded with the two decisions that are not obvious: the pick is scoped to the TAB, since series keys are ids and the same project is the same id on every chart that knows it; and a chart with NO mark for the key is left untouched rather than dimmed whole, because a chart with nothing lit reads as absent data. Marks carry a second key where they stand for two series at once, and marks belonging to the MONTH - thresholds, baselines, the V-34 outline - carry none and never fade. Sheet 03 records COLUMN_LABEL beside COLUMN_HELP: a plain name for every column, shown above the column's own name in each heading. Nothing is renamed, the schema stays at 11, validation messages still name the column, and the cell still writes back through the identifier - the label is a second line, not a substitution. Sheet 07 records the one mechanical consequence: a test reading a column name off a heading must read the identifier line, not the heading's text. Written against plan v2.53.</t>
+          <t>R-45, REQ-DSH-16. Five screen changes, no rule and no figure. Sheet 06 records the four that are drawing decisions. A CHART WHOSE X AXIS IS THE HORIZON takes its width from the month count - W = max(Wmin, padL + padR + months x Wper) - and its panel scrolls; the two utilisation charts were the last fixed-width ones, and a fixed width is legible only over the span it was chosen for and fails silently outside it. Wper is chosen so the DEFAULT horizon still falls under Wmin, which is what keeps the change invisible to the view almost everybody opens on. PANELS ARE TILED ONLY WHERE BOTH ARE NARROW: the person tab's three wide tables are one column, in work order. A PANEL THAT IS A CHILD OF A SELECTION names its parent from one shared helper, so two panels stating the same assignment cannot drift. LEGEND PICKING is recorded with the two decisions that are not obvious: the pick is scoped to the TAB, since series keys are ids and the same project is the same id on every chart that knows it; and a chart with NO mark for the key is left untouched rather than dimmed whole, because a chart with nothing lit reads as absent data. Marks carry a second key where they stand for two series at once, and marks belonging to the MONTH - thresholds, baselines, the V-34 outline - carry none and never fade. Sheet 03 records COLUMN_LABEL beside COLUMN_HELP: a plain name for every column, and it is now the WHOLE of what a heading prints. The column's own name went on a second line for one release and was taken off at review: the need for it is occasional - editing the workbook, chasing a finding - and a heading is read on every glance, so it belongs in the pop-up, which every heading now carries, and on the element as data-cid. Nothing is renamed, the schema stays at 11, validation messages still name the column, and the cell still writes back through the identifier. Sheet 07 records the one mechanical consequence: a test reading a column name off a heading reads data-cid, not the heading's text. Written against plan v2.53.</t>
         </is>
       </c>
       <c r="F7" s="10" t="inlineStr">
@@ -4627,7 +4627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E148"/>
+  <dimension ref="A1:E158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -6075,95 +6075,161 @@
     <row r="134">
       <c r="A134" s="6" t="inlineStr">
         <is>
-          <t>plain name for it. Each table heading shows the plain name above the column's own name, and the same</t>
+          <t>plain name for it. A table heading prints the PLAIN NAME AND NOTHING ELSE; the column's own name is</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="6" t="inlineStr">
         <is>
-          <t>two-part head opens the heading's pop-up, every cell's, and the filter buttons'.</t>
+          <t>in the heading's pop-up and on the element as data-cid. The same two-part head - plain name, then</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="6" t="inlineStr"/>
+      <c r="A136" s="6" t="inlineStr">
+        <is>
+          <t>column name in the quieter type - opens the heading's pop-up, every cell's, and the filter buttons'.</t>
+        </is>
+      </c>
     </row>
     <row r="137">
-      <c r="A137" s="6" t="inlineStr">
-        <is>
-          <t>THIS IS NOT A RENAME. The workbook's column names stay on screen, stay in every validation message,</t>
-        </is>
-      </c>
+      <c r="A137" s="6" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="6" t="inlineStr">
         <is>
-          <t>and stay as the key the editing path writes back through (data-col on the cell is the identifier,</t>
+          <t>WHERE THE IDENTIFIER BELONGS WAS SETTLED TWICE, and the reasoning is recorded because the first</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="6" t="inlineStr">
         <is>
-          <t>never the label). The schema is unchanged at 11 and no file is affected. What changes is that a</t>
+          <t>answer was defensible and still wrong. It was printed on a second line under the label, on the</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="6" t="inlineStr">
         <is>
-          <t>reader who has never seen this document can now read the table: work_scope_type, outsourcing_scope_det,</t>
+          <t>argument that the screen and the file are the same thing, so a heading must be findable in the</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="6" t="inlineStr">
         <is>
-          <t>absorbed_by and ref_id were legible to whoever wrote the schema and to nobody else, and their meaning</t>
+          <t>spreadsheet, quotable in a mail and lookup-able here. Right about the need, wrong about the place:</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="6" t="inlineStr">
         <is>
-          <t>lived in a pop-up - which is to say it was there only for a reader who already knew to hover.</t>
+          <t>looking a column name up is OCCASIONAL - editing the workbook, chasing a finding - and a heading is</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="6" t="inlineStr"/>
+      <c r="A143" s="6" t="inlineStr">
+        <is>
+          <t>read on EVERY glance by everyone, so printing it charged the common case for the rare one while the</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="6" t="inlineStr">
         <is>
-          <t>COLUMN_LABEL must cover every column in SHEET_HEADERS, plus the read-only lookup columns the</t>
+          <t>pop-up already answered it in full.</t>
         </is>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="6" t="inlineStr">
-        <is>
-          <t>application adds beside them (standard_fte, automatic_fte, difference, period, sharers). A missing</t>
-        </is>
-      </c>
+      <c r="A145" s="6" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="6" t="inlineStr">
         <is>
-          <t>entry is not an error - the heading falls back to the bare identifier - which is exactly why it is</t>
+          <t>THIS IS NOT A RENAME. The workbook's column names stay in every validation message, stay reachable</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="6" t="inlineStr">
         <is>
-          <t>held by a test rather than left to notice: a silent fallback to the old behaviour is the failure</t>
+          <t>from every heading, and stay as the key the editing path writes back through (data-col on the cell is</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="6" t="inlineStr">
+        <is>
+          <t>the identifier, never the label). The schema is unchanged at 11 and no file is affected. What changes</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="6" t="inlineStr">
+        <is>
+          <t>is that a reader who has never seen this document can now read the table: work_scope_type,</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="6" t="inlineStr">
+        <is>
+          <t>outsourcing_scope_det, absorbed_by and ref_id were legible to whoever wrote the schema and to nobody</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="6" t="inlineStr">
+        <is>
+          <t>else, and their meaning lived in a pop-up - which is to say it was there only for a reader who</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="6" t="inlineStr">
+        <is>
+          <t>already knew to hover.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="6" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="6" t="inlineStr">
+        <is>
+          <t>COLUMN_LABEL must cover every column in SHEET_HEADERS, plus the read-only lookup columns the</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="6" t="inlineStr">
+        <is>
+          <t>application adds beside them (standard_fte, automatic_fte, difference, period, sharers). A missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="6" t="inlineStr">
+        <is>
+          <t>entry is not an error - the heading falls back to the bare identifier - which is exactly why it is</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="6" t="inlineStr">
+        <is>
+          <t>held by a test rather than left to notice: a silent fallback to the old behaviour is the failure</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="6" t="inlineStr">
         <is>
           <t>mode this replaces. tools/test_labels.py checks the map against the schema, not against the screen.</t>
         </is>
@@ -10526,12 +10592,12 @@
     <row r="101">
       <c r="A101" s="8" t="inlineStr">
         <is>
-          <t>Headings carry two lines</t>
+          <t>A heading is the plain name</t>
         </is>
       </c>
       <c r="B101" s="9" t="inlineStr">
         <is>
-          <t>Every column heading shows a PLAIN NAME above the column's own name. The workbook's column names must stay on screen - the screen and the file are the same thing, so a heading is something to find in the spreadsheet, quote in a mail and look up in this document - and they are not, by themselves, labels: work_scope_type, outsourcing_scope_det, absorbed_by and ref_id are legible to whoever wrote the schema and opaque to whoever fills the plan in. The meaning existed, in the heading's pop-up, which is to say it existed only for a reader who knew to hover. NOTHING IS RENAMED: the schema is unchanged, validation messages still name the column, and the cell still writes back through the identifier - the plain name is a second line, never a substitution. The same two-part head is used on the heading's pop-up, on every cell's and on the filter buttons', so it is learned once. COLUMN_LABEL sits beside COLUMN_HELP in the parse module, so a column gets a sentence and a name in the same place.</t>
+          <t>Every column heading shows a PLAIN NAME and nothing else. work_scope_type, outsourcing_scope_det, absorbed_by and ref_id are legible to whoever wrote the schema and opaque to whoever fills the plan in, and their meaning existed only in the heading's pop-up - which is to say only for a reader who knew to hover. THE COLUMN'S OWN NAME IS IN THE POP-UP AND ON THE ELEMENT, NOT ON THE PAGE, and the reasoning is worth recording because it was settled twice. The first attempt put it on a second line under the label, on the argument that the screen and the file are the same thing, so a heading must be findable in the spreadsheet. That argument is right about the need and wrong about the place: looking up a column name is OCCASIONAL - editing the workbook, chasing a finding - and a heading is read on EVERY glance, so printing it charged the common case for the rare one when the pop-up already answered it. Every heading therefore carries a pop-up naming both, and the identifier as data-cid for whatever must read it. A badge that names another column ('sets ...') uses that column's plain name too, since a heading row that has stopped printing identifiers must not keep one in a badge. NOTHING IS RENAMED: the schema is unchanged, validation messages still name the column, and the cell still writes back through the identifier. The same two-part head is used on the heading's pop-up, on every cell's and on the filter buttons', so it is learned once. COLUMN_LABEL sits beside COLUMN_HELP in the parse module, so a column gets a sentence and a name in the same place.</t>
         </is>
       </c>
       <c r="C101" s="8" t="inlineStr">
